--- a/tests/yuhi/reaction_network.xlsx
+++ b/tests/yuhi/reaction_network.xlsx
@@ -1055,8 +1055,10 @@
         <v>18</v>
       </c>
       <c r="G3" s="2"/>
-      <c r="H3" s="4" t="s">
-        <v>156</v>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>read:33COS_OH_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -1077,8 +1079,10 @@
         <v>19</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="4" t="s">
-        <v>156</v>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>read:34COS_OH_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -1099,8 +1103,10 @@
         <v>20</v>
       </c>
       <c r="G5" s="3"/>
-      <c r="H5" s="4" t="s">
-        <v>156</v>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>read:36COS_OH_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1143,8 +1149,10 @@
         <v>24</v>
       </c>
       <c r="G7" s="3"/>
-      <c r="H7" s="4" t="s">
-        <v>156</v>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>read:33COS_O_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1165,8 +1173,10 @@
         <v>26</v>
       </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="4" t="s">
-        <v>156</v>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>read:34COS_O_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1187,8 +1197,10 @@
         <v>27</v>
       </c>
       <c r="G9" s="3"/>
-      <c r="H9" s="4" t="s">
-        <v>156</v>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>read:36COS_O_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -3583,8 +3595,10 @@
       </c>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
-      <c r="H118" s="3" t="s">
-        <v>156</v>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>read:32SO2_OH_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -3603,8 +3617,10 @@
       </c>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
-      <c r="H119" s="3" t="s">
-        <v>156</v>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>read:33SO2_OH_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
@@ -3623,8 +3639,10 @@
       </c>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
-      <c r="H120" s="3" t="s">
-        <v>156</v>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>read:34SO2_OH_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -3643,8 +3661,10 @@
       </c>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
-      <c r="H121" s="3" t="s">
-        <v>156</v>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>read:36SO2_OH_rate.txt</t>
+        </is>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -4353,8 +4373,10 @@
       <c r="G154" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H154" s="3" t="s">
-        <v>156</v>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>read:32H2SO4_photorate.txt</t>
+        </is>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -4375,8 +4397,10 @@
       <c r="G155" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H155" s="3" t="s">
-        <v>156</v>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>read:33H2SO4_photorate.txt</t>
+        </is>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -4397,8 +4421,10 @@
       <c r="G156" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H156" s="3" t="s">
-        <v>156</v>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>read:34H2SO4_photorate.txt</t>
+        </is>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -4419,8 +4445,10 @@
       <c r="G157" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H157" s="3" t="s">
-        <v>156</v>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>read:36H2SO4_photorate.txt</t>
+        </is>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
